--- a/attached_assets/list_books.xlsx
+++ b/attached_assets/list_books.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\b_outside\a_intesa_global_technology\Storify\Storify-Insights\Storify-Insights\attached_assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{22D413EA-82C0-487F-A71B-3FF7AB523C69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDC4B103-EB33-406B-B9A3-3881A4C712FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15264" yWindow="0" windowWidth="15552" windowHeight="16656" xr2:uid="{61CDC90C-EC06-4A7D-B103-BEBAB272D490}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{61CDC90C-EC06-4A7D-B103-BEBAB272D490}"/>
   </bookViews>
   <sheets>
     <sheet name="list_books" sheetId="1" r:id="rId1"/>
@@ -2112,8 +2112,9 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="7"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -2489,7 +2490,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C3B5F0C-30FD-4D4F-833B-29A0E965B1BE}">
-  <dimension ref="A1:E226"/>
+  <dimension ref="A1:F226"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="51.5546875" customWidth="1"/>
@@ -2769,7 +2770,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>261</v>
       </c>
@@ -2786,7 +2787,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>37</v>
       </c>
@@ -2803,7 +2804,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>204</v>
       </c>
@@ -2820,7 +2821,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>181</v>
       </c>
@@ -2837,7 +2838,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>195</v>
       </c>
@@ -2854,24 +2855,25 @@
         <v>184</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="D22">
+      <c r="D22" s="1">
         <v>394</v>
       </c>
-      <c r="E22" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E22" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F22" s="1"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>185</v>
       </c>
@@ -2888,7 +2890,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>188</v>
       </c>
@@ -2905,7 +2907,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>193</v>
       </c>
@@ -2922,7 +2924,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>540</v>
       </c>
@@ -2939,7 +2941,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>39</v>
       </c>
@@ -2956,7 +2958,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>44</v>
       </c>
@@ -2973,7 +2975,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>197</v>
       </c>
@@ -2990,7 +2992,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>200</v>
       </c>
@@ -3007,7 +3009,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>201</v>
       </c>
@@ -3024,7 +3026,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>533</v>
       </c>

--- a/attached_assets/list_books.xlsx
+++ b/attached_assets/list_books.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\b_outside\a_intesa_global_technology\Storify\Storify-Insights\Storify-Insights\attached_assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDC4B103-EB33-406B-B9A3-3881A4C712FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFEE881D-7CF6-459E-A842-AD682CC2F94C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{61CDC90C-EC06-4A7D-B103-BEBAB272D490}"/>
+    <workbookView xWindow="15264" yWindow="0" windowWidth="15552" windowHeight="16656" xr2:uid="{61CDC90C-EC06-4A7D-B103-BEBAB272D490}"/>
   </bookViews>
   <sheets>
     <sheet name="list_books" sheetId="1" r:id="rId1"/>
@@ -1771,7 +1771,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1951,6 +1951,12 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="10">
     <border>
@@ -2112,9 +2118,10 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="7"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -4231,7 +4238,7 @@
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A103" t="s">
+      <c r="A103" s="2" t="s">
         <v>298</v>
       </c>
       <c r="B103" t="s">
@@ -4673,7 +4680,7 @@
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A129" t="s">
+      <c r="A129" s="2" t="s">
         <v>328</v>
       </c>
       <c r="B129" t="s">
@@ -4826,7 +4833,7 @@
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A138" t="s">
+      <c r="A138" s="2" t="s">
         <v>403</v>
       </c>
       <c r="B138" t="s">
@@ -4860,7 +4867,7 @@
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A140" t="s">
+      <c r="A140" s="2" t="s">
         <v>343</v>
       </c>
       <c r="B140" t="s">
@@ -4877,7 +4884,7 @@
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A141" t="s">
+      <c r="A141" s="2" t="s">
         <v>340</v>
       </c>
       <c r="B141" t="s">
@@ -5129,7 +5136,7 @@
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A156" t="s">
+      <c r="A156" s="2" t="s">
         <v>530</v>
       </c>
       <c r="B156" t="s">
@@ -5605,7 +5612,7 @@
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A184" t="s">
+      <c r="A184" s="2" t="s">
         <v>417</v>
       </c>
       <c r="B184" t="s">
@@ -5639,7 +5646,7 @@
       </c>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A186" t="s">
+      <c r="A186" s="2" t="s">
         <v>421</v>
       </c>
       <c r="B186" t="s">
@@ -5979,7 +5986,7 @@
       </c>
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A206" t="s">
+      <c r="A206" s="2" t="s">
         <v>444</v>
       </c>
       <c r="B206" t="s">
@@ -6166,7 +6173,7 @@
       </c>
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A217" t="s">
+      <c r="A217" s="2" t="s">
         <v>457</v>
       </c>
       <c r="B217" t="s">
@@ -6251,7 +6258,7 @@
       </c>
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A222" t="s">
+      <c r="A222" s="2" t="s">
         <v>474</v>
       </c>
       <c r="B222" t="s">
@@ -6302,7 +6309,7 @@
       </c>
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A225" t="s">
+      <c r="A225" s="2" t="s">
         <v>481</v>
       </c>
       <c r="B225" t="s">
